--- a/table/supp/workbooks/SuppTable_S9_LINEX_reaction_mapping.xlsx
+++ b/table/supp/workbooks/SuppTable_S9_LINEX_reaction_mapping.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">Reaction_ID</t>
   </si>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">paired Wilcoxon signed-rank</t>
   </si>
   <si>
-    <t xml:space="preserve">products_enriched_in_LI</t>
+    <t xml:space="preserve">products_enriched_in_LIN</t>
   </si>
   <si>
     <t xml:space="preserve">log10(DG) - log10(TG)</t>
   </si>
   <si>
-    <t xml:space="preserve">substrates_enriched_in_LI</t>
+    <t xml:space="preserve">substrates_enriched_in_LIN</t>
   </si>
   <si>
     <t xml:space="preserve">mean(log10(TG),log10(LPE)) - mean(log10(PE),log10(DG))</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">GeneID</t>
   </si>
   <si>
-    <t xml:space="preserve">Role_label</t>
+    <t xml:space="preserve">Gene_family</t>
   </si>
   <si>
     <t xml:space="preserve">annotation</t>
@@ -179,15 +179,15 @@
     <t xml:space="preserve">GWAS_type</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
     <t xml:space="preserve">Best_SNP</t>
   </si>
   <si>
     <t xml:space="preserve">Best_P_Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Max_r2</t>
+  </si>
+  <si>
     <t xml:space="preserve">N_Phenotypes</t>
   </si>
   <si>
@@ -197,28 +197,22 @@
     <t xml:space="preserve">linked_fraction</t>
   </si>
   <si>
-    <t xml:space="preserve">N_direct_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct_ratio_fraction</t>
+    <t xml:space="preserve">Phenotypes</t>
   </si>
   <si>
     <t xml:space="preserve">linked_examples</t>
   </si>
   <si>
-    <t xml:space="preserve">direct_ratio_examples</t>
-  </si>
-  <si>
     <t xml:space="preserve">LCAT* (PC+DG &lt;-&gt; LPC+TG)</t>
   </si>
   <si>
-    <t xml:space="preserve">SORBI_3001G103800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCAT-like 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lecithin-cholesterol acyltransferase-like 1;SORBI_3001G103800;PTN004259986;orthologs</t>
+    <t xml:space="preserve">SORBI_3004G341900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCAT/PSAT superfamily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phospholipid--sterol O-acyltransferase</t>
   </si>
   <si>
     <t xml:space="preserve">LIN</t>
@@ -227,85 +221,85 @@
     <t xml:space="preserve">Individual</t>
   </si>
   <si>
-    <t xml:space="preserve">S8_lowinput</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_7987166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC(18:2_20:4); TG(14:0_18:3_18:3)</t>
+    <t xml:space="preserve">SNP_67264279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA(22:1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3006G214500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecithin-cholesterol acyltransferase-like 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_56256983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG(18:2_18:3); MG(18:2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG(18:2_18:3)</t>
   </si>
   <si>
     <t xml:space="preserve">SumRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">S9_lowinput</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_DG_over_AEG_log10safe; Sum_DG_over_DGDG_log10safe; Sum_DG_over_GalCer_log10safe; Sum_DG_over_LPC_log10safe; Sum_DG_over_LPE_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_DG_over_LPC_log10safe; Sum_DG_over_TG_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3001G448800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCAT-like 1 paralog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lecithin-cholesterol acyltransferase-like 1;SORBI_3001G448800;PTN004259905;orthologs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_72626995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3006G214500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCAT-like 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lecithin-cholesterol acyltransferase-like 4;SORBI_3006G214500;PTN004259842;orthologs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_56290997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG(18:2_18:3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_56307749</t>
+    <t xml:space="preserve">FA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNPLA1 branch (TG &lt;-&gt; DG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3003G389400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNPLA/patatin lipase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patatin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_70096409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA(22:1); PC(18:2_20:4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3002G031800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_2818333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,14,17-Eicosatrienoic acid,(Z,Z,Z)-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3007G158600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_59520764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,14,17-Eicosatrienoic acid,(Z,Z,Z)-; FA(22:1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3005G144300</t>
   </si>
   <si>
     <t xml:space="preserve">CTL</t>
   </si>
   <si>
-    <t xml:space="preserve">S9_control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_7972773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_PC_over_PE_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_72605500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_PC_over_GalCer_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNPLA1 branch (TG &lt;-&gt; DG)</t>
+    <t xml:space="preserve">SNP_60968355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG(16:0_16:0_20:1); TG(16:0_18:1_18:1); TG(16:0_18:1_20:0); TG(18:0_18:2_18:2)</t>
   </si>
   <si>
     <t xml:space="preserve">SORBI_3001G041900</t>
   </si>
   <si>
-    <t xml:space="preserve">PNPLA-domain TAG lipase-like</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNPLA domain-containing protein;SORBI_3001G041900;PTN004457248;orthologs</t>
+    <t xml:space="preserve">PNPLA domain-containing protein</t>
   </si>
   <si>
     <t xml:space="preserve">SNP_3152951</t>
@@ -314,67 +308,64 @@
     <t xml:space="preserve">TG(16:1_20:1_20:2); TG(18:1_18:2_22:0); TG(18:2_18:3_20:3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum_SM_over_TG_log10safe; Sum_SQDG_over_TG_log10safe; Sum_TG_over_SM_log10safe; Sum_TG_over_SQDG_log10safe; TG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3010G270700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDSL esterase/lipase-like</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDSL esterase_lipase;SORBI_3010G270700;PTN005223057;orthologs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_60513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_LPC_over_TG_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S8_control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_3133155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG-DG synthesis arm</t>
+    <t xml:space="preserve">SORBI_3008G166050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_59963149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGTS(34:5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3001G157900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_12695170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13-Keto-9Z,11E-octadecadienoic acid; 13S-HOTrE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3001G158200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNPLA3 branch (DG+MG &lt;-&gt; TG)</t>
   </si>
   <si>
     <t xml:space="preserve">SORBI_3010G170000</t>
   </si>
   <si>
-    <t xml:space="preserve">DGAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O-acyltransferase;SORBI_3010G170000;PTN004157788;orthologs</t>
+    <t xml:space="preserve">DGAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-acyltransferase</t>
   </si>
   <si>
     <t xml:space="preserve">SNP_50134510</t>
   </si>
   <si>
-    <t xml:space="preserve">TG(18:1_18:3_22:0); TG(18:1_20:3_22:0); TG(18:2_18:2_18:4); TG(18:2_20:3_22:0); TG(18:3_18:3_18:3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_50111070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum_Cer_over_DG_log10safe; Sum_Cer_over_TG_log10safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3009G034600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGAT-like</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diacylglycerol acyltransferase;SORBI_3009G034600;;orthologs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNP_3190673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG(14:0_18:1_18:3); TG(18:1_18:2_18:2)</t>
+    <t xml:space="preserve">11,14,17-Eicosatrienoic acid,(Z,Z,Z)-; TG(18:1_18:3_22:0); TG(18:2_18:2_18:4); TG(18:2_20:2_22:2); TG(18:2_20:3_22:0); TG(18:3_18:3_18:3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG(18:1_18:3_22:0); TG(18:2_18:2_18:4); TG(18:2_20:2_22:2); TG(18:2_20:3_22:0); TG(18:3_18:3_18:3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3009G072700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_8962578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,14,17-Eicosatrienoic acid,(Z,Z,Z)-; PC(18:2_20:4); TG(14:0_18:3_18:3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG(14:0_18:3_18:3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNP_8966031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cer</t>
   </si>
   <si>
     <t xml:space="preserve">N_genes_with_hits</t>
@@ -386,9 +377,6 @@
     <t xml:space="preserve">Total_N_linked</t>
   </si>
   <si>
-    <t xml:space="preserve">Total_N_direct_ratio</t>
-  </si>
-  <si>
     <t xml:space="preserve">median_linked_fraction</t>
   </si>
   <si>
@@ -398,16 +386,19 @@
     <t xml:space="preserve">Genes</t>
   </si>
   <si>
-    <t xml:space="preserve">SORBI_3001G103800; SORBI_3001G448800; SORBI_3006G214500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3001G103800; SORBI_3001G448800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3001G041900; SORBI_3010G270700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SORBI_3010G170000; SORBI_3009G034600</t>
+    <t xml:space="preserve">SORBI_3004G341900; SORBI_3006G214500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRO1 branch (PE+DG &lt;-&gt; TG+LPE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3001G041900; SORBI_3001G157900; SORBI_3001G158200; SORBI_3002G031800; SORBI_3003G389400; SORBI_3007G158600; SORBI_3008G166050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORBI_3009G072700; SORBI_3010G170000</t>
   </si>
 </sst>
 </file>
@@ -911,31 +902,31 @@
         <v>355</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.56217103096993</v>
+        <v>-1.47332485748076</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.32428389853272</v>
+        <v>-1.33432268504072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.237887132437216</v>
+        <v>0.139002172440045</v>
       </c>
       <c r="G2" t="s">
         <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000223999317911119</v>
+        <v>0.0000000000000000000000000000000000000000000000000000518535962478624</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000447998635822237</v>
+        <v>0.0000000000000000000000000000000000000000000000000000518535962478624</v>
       </c>
       <c r="J2" t="s">
         <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0192105928224353</v>
+        <v>0.120448713087555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.471251971253989</v>
+        <v>0.155416870428828</v>
       </c>
     </row>
     <row r="3">
@@ -949,31 +940,31 @@
         <v>355</v>
       </c>
       <c r="D3" t="n">
-        <v>0.737923912739001</v>
+        <v>0.737875176469983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.469717886895582</v>
+        <v>0.482065559835954</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.268206025843419</v>
+        <v>-0.255809616634029</v>
       </c>
       <c r="G3" t="s">
         <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000160659130968592</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000311664772451548</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000160659130968592</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000415553029935397</v>
       </c>
       <c r="J3" t="s">
         <v>46</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.552538852153419</v>
+        <v>-0.274357962518654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.019745715099464</v>
+        <v>-0.24029609248288</v>
       </c>
     </row>
     <row r="4">
@@ -987,31 +978,31 @@
         <v>355</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.74616914914411</v>
+        <v>-1.83199940546888</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.51396727927399</v>
+        <v>-1.57069061443188</v>
       </c>
       <c r="F4" t="n">
-        <v>0.232201869870121</v>
+        <v>0.261308791037008</v>
       </c>
       <c r="G4" t="s">
         <v>43</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000962883206586764</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000799374775003856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000385153282634706</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000319749910001542</v>
       </c>
       <c r="J4" t="s">
         <v>44</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0586908885768039</v>
+        <v>0.249594132977648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.459582862418349</v>
+        <v>0.281102781172614</v>
       </c>
     </row>
     <row r="5">
@@ -1025,31 +1016,31 @@
         <v>355</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.23300794540501</v>
+        <v>-0.233675103794599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0935194394174355</v>
+        <v>0.0803652654438389</v>
       </c>
       <c r="F5" t="n">
-        <v>0.326527384822445</v>
+        <v>0.314040369238438</v>
       </c>
       <c r="G5" t="s">
         <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000073949765003737</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000110596577877976</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000985996866716493</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000221193155755952</v>
       </c>
       <c r="J5" t="s">
         <v>44</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0274485825115204</v>
+        <v>0.299782806447882</v>
       </c>
       <c r="L5" t="n">
-        <v>0.601726555315359</v>
+        <v>0.33498889494698</v>
       </c>
     </row>
   </sheetData>
@@ -1106,138 +1097,120 @@
       <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="O1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P1" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>67</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>68</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="n">
+        <v>0.0000000000007555142</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.788978</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
         <v>69</v>
       </c>
-      <c r="G2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.00000000000313</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2"/>
+      <c r="N2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
         <v>64</v>
       </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>67</v>
       </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0000000003856837</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="s">
         <v>73</v>
       </c>
-      <c r="G3" t="s">
+      <c r="N3" t="s">
         <v>74</v>
-      </c>
-      <c r="H3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.00000000000313</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="O3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
         <v>64</v>
       </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
         <v>68</v>
       </c>
-      <c r="F4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" t="s">
-        <v>80</v>
+      <c r="H4" t="n">
+        <v>0.000000005508909</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000000000253</v>
+        <v>0.665499</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1248,90 +1221,80 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="M4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
         <v>81</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="n">
+        <v>0.000000000001905507</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>82</v>
       </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.000000000411</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>85</v>
-      </c>
-      <c r="P5"/>
+      <c r="N5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.000000000009538726</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0000000832</v>
+        <v>0.756085</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1342,282 +1305,252 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
+      <c r="M6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>67</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>87</v>
       </c>
-      <c r="F7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="n">
+        <v>0.0000000001945536</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.472621</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
         <v>88</v>
       </c>
-      <c r="H7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.000000065</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>90</v>
-      </c>
-      <c r="P7"/>
+      <c r="N7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" t="s">
         <v>91</v>
       </c>
+      <c r="H8" t="n">
+        <v>0.0000000003098264</v>
+      </c>
       <c r="I8" t="n">
-        <v>0.0000000763</v>
+        <v>0.507024</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="M8" t="s">
         <v>92</v>
       </c>
-      <c r="P8"/>
+      <c r="N8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" t="s">
-        <v>97</v>
+        <v>81</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0000000007789776</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00000000113</v>
+        <v>0.73676</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>98</v>
-      </c>
-      <c r="P9"/>
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
         <v>93</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
         <v>94</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" t="s">
         <v>95</v>
       </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>97</v>
+      <c r="H10" t="n">
+        <v>0.000000001127564</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00000000202</v>
+        <v>0.776994</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>99</v>
-      </c>
-      <c r="P10"/>
+      <c r="M10" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.000000006038522</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000000307</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11"/>
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.000000006283125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0000000147</v>
+        <v>0.423424</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -1628,158 +1561,182 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12"/>
-      <c r="P12"/>
+      <c r="M12" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" t="s">
-        <v>111</v>
+        <v>101</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.000000006283125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00000000000000316</v>
+        <v>0.451094</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>112</v>
-      </c>
-      <c r="P13"/>
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
         <v>107</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
         <v>108</v>
       </c>
-      <c r="C14" t="s">
+      <c r="H14" t="n">
+        <v>0.000000000000003159062</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M14" t="s">
         <v>109</v>
       </c>
-      <c r="D14" t="s">
+      <c r="N14" t="s">
         <v>110</v>
       </c>
-      <c r="E14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.000000000276</v>
-      </c>
-      <c r="J14" t="n">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>114</v>
-      </c>
-      <c r="P14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
         <v>107</v>
       </c>
-      <c r="B15" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.000000000008390241</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00000000175</v>
+        <v>0.426266</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>119</v>
-      </c>
-      <c r="P15"/>
+        <v>0.333</v>
+      </c>
+      <c r="M15" t="s">
+        <v>113</v>
+      </c>
+      <c r="N15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.000000004320659</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+      <c r="N16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1800,170 +1757,146 @@
         <v>52</v>
       </c>
       <c r="C1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>121</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>122</v>
-      </c>
-      <c r="F1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.00000000000313</v>
-      </c>
-      <c r="I2" t="s">
-        <v>127</v>
+        <v>0.0000000000007555142</v>
+      </c>
+      <c r="H2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.000000065</v>
-      </c>
-      <c r="I3" t="s">
-        <v>128</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.00000000113</v>
-      </c>
-      <c r="I4" t="s">
-        <v>129</v>
+        <v>0.0000000003098264</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0000000147</v>
-      </c>
-      <c r="I5" t="s">
-        <v>94</v>
+        <v>0.000000000001905507</v>
+      </c>
+      <c r="H5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.00000000000000316</v>
-      </c>
-      <c r="I6" t="s">
-        <v>130</v>
+        <v>0.000000000000003159062</v>
+      </c>
+      <c r="H6" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
